--- a/www/flightdata/xlsx/eoss-372.xlsx
+++ b/www/flightdata/xlsx/eoss-372.xlsx
@@ -3741,7 +3741,7 @@
         <v>27814.22</v>
       </c>
       <c r="I2">
-        <v>652</v>
+        <v>487</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
